--- a/assets/constructions/examples/ctd_mie_per.xlsx
+++ b/assets/constructions/examples/ctd_mie_per.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE6"/>
+  <dimension ref="A1:AI6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,6 +584,26 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -687,11 +707,17 @@
           <t>2019 / DEREK</t>
         </is>
       </c>
+      <c r="AF2" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>MT190B-032Z25R02BD10-L125-IK</t>
+          <t>MT190B-030W25R02BD10-L125-IK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -701,12 +727,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>MT190B-Z...BD10-IK</t>
+          <t>MT190B-W...BD10-IK</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" t="n">
         <v>25</v>
@@ -730,7 +756,7 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="n">
-        <v>34000</v>
+        <v>37200</v>
       </c>
       <c r="P3" t="n">
         <v>0.6</v>
@@ -740,7 +766,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -753,7 +779,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>HA-25</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -788,65 +814,71 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AF3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ASJ-C32-32-200-4T</t>
+          <t>MT190B-020W20R01BD08</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DEREK</t>
+          <t>СКИФ-М</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ASJ</t>
+          <t>MT190B-W...</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="F4" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="G4" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="H4" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L4" t="n">
         <v>1</v>
       </c>
-      <c r="M4" t="b">
-        <v>0</v>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="O4" t="n">
+        <v>30000</v>
+      </c>
       <c r="P4" t="n">
-        <v>1.25</v>
+        <v>0.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>HA</t>
+          <t>HB</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>APMT160408L/APMT150408R</t>
+          <t>BDMT08030.R</t>
         </is>
       </c>
       <c r="T4" t="n">
@@ -854,19 +886,19 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>HA-32</t>
+          <t>HB-20</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>DER_AP1604H-L+DER_AP1504H-R</t>
+          <t>SKIF_BD0803H</t>
         </is>
       </c>
       <c r="W4" t="n">
+        <v>1</v>
+      </c>
+      <c r="X4" t="n">
         <v>2</v>
-      </c>
-      <c r="X4" t="n">
-        <v>8</v>
       </c>
       <c r="Y4" t="n">
         <v>90</v>
@@ -877,25 +909,29 @@
       <c r="AA4" t="n">
         <v>0</v>
       </c>
-      <c r="AB4" t="n">
-        <v>31.8</v>
-      </c>
+      <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>AP1604_H/AP1504_H</t>
+          <t>SKIF_BD0803H</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>2019 / DEREK</t>
-        </is>
-      </c>
+          <t>2019/ Основной каталог СКИФ-М</t>
+        </is>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>MT190B-040W32R02BD16</t>
+          <t>MT190B-030W25R02BD10-R5-L125-IK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -905,21 +941,21 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MT190B-W...</t>
+          <t>MT190B-W...BD10-R5-IK</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F5" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="G5" t="n">
-        <v>110</v>
+        <v>125</v>
       </c>
       <c r="H5" t="n">
-        <v>50</v>
+        <v>69</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
@@ -934,13 +970,13 @@
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>17000</v>
+        <v>37200</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -949,20 +985,20 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>BDMT160508ER + BDMT120408ER</t>
+          <t>BDHX10T350FR + BDHT10T330FR</t>
         </is>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>HB-32</t>
+          <t>HB-25</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>SKIF_BD1605H + SKIF_BD1204H</t>
+          <t>SKIF_BD10T3H</t>
         </is>
       </c>
       <c r="W5" t="n">
@@ -975,15 +1011,15 @@
         <v>90</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>SKIF_BD1605H + SKIF_BD1204H</t>
+          <t>SKIF_BD10T3H</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr"/>
@@ -992,11 +1028,17 @@
           <t>2019/ Основной каталог СКИФ-М</t>
         </is>
       </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ASJ-C32-32-300-4T</t>
+          <t>ASJ-C32-35-300-4T</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1011,7 +1053,7 @@
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F6" t="n">
         <v>32</v>
@@ -1038,10 +1080,10 @@
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>24</v>
+        <v>25.5</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -1050,7 +1092,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>APMT160408L/APMT150408R</t>
+          <t>APMT170408L/APMT150408R</t>
         </is>
       </c>
       <c r="T6" t="n">
@@ -1063,7 +1105,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>DER_AP1604H-L+DER_AP1504H-R</t>
+          <t>DER_AP1704H-L+DER_AP1504H-R</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1086,7 +1128,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>AP1604_H/AP1504_H</t>
+          <t>AP1704_H/AP1504_H</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr"/>
@@ -1095,6 +1137,12 @@
           <t>2019 / DEREK</t>
         </is>
       </c>
+      <c r="AF6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
